--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:08:00+00:00</t>
+    <t>2025-05-12T08:18:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:18:40+00:00</t>
+    <t>2025-05-12T08:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:26:30+00:00</t>
+    <t>2025-05-12T09:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,11 +709,11 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t>pattern:system}
-pattern:type}</t>
-  </si>
-  <si>
-    <t>Slice based on the identifier.system pattern</t>
+    <t>value:system}
+value:type}</t>
+  </si>
+  <si>
+    <t>Slice based on the identifier.system #value</t>
   </si>
   <si>
     <t xml:space="preserve">org-1
@@ -1384,10 +1384,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -12383,7 +12379,7 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>437</v>
+        <v>140</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -12408,27 +12404,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>78</v>
@@ -12491,7 +12487,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -12524,24 +12520,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12650,10 +12646,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12764,10 +12760,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12880,10 +12876,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12992,10 +12988,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13106,10 +13102,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13222,10 +13218,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13336,10 +13332,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13365,7 +13361,7 @@
         <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>370</v>
@@ -13450,10 +13446,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13564,10 +13560,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13680,10 +13676,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13796,13 +13792,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
@@ -13827,7 +13823,7 @@
         <v>240</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>432</v>
@@ -13865,7 +13861,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -13898,24 +13894,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14024,10 +14020,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14138,10 +14134,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14254,10 +14250,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14366,10 +14362,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14480,10 +14476,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14596,10 +14592,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14710,10 +14706,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14739,7 +14735,7 @@
         <v>168</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>370</v>
@@ -14824,10 +14820,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14938,10 +14934,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15054,10 +15050,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15170,13 +15166,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>430</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>78</v>
@@ -15201,7 +15197,7 @@
         <v>240</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>432</v>
@@ -15239,7 +15235,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15272,24 +15268,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15398,10 +15394,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15512,10 +15508,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15628,10 +15624,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15740,10 +15736,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15854,10 +15850,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15970,10 +15966,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16084,10 +16080,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16113,7 +16109,7 @@
         <v>168</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>370</v>
@@ -16198,10 +16194,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16312,10 +16308,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16428,10 +16424,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16544,10 +16540,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16573,16 +16569,16 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16631,7 +16627,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16646,13 +16642,13 @@
         <v>100</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL126" t="s" s="2">
+      <c r="AM126" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -16660,10 +16656,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16689,16 +16685,16 @@
         <v>102</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -16747,7 +16743,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16765,7 +16761,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -16776,10 +16772,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16802,19 +16798,19 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -16863,7 +16859,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16872,19 +16868,19 @@
         <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AJ128" t="s" s="2">
+      <c r="AK128" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AK128" t="s" s="2">
+      <c r="AL128" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AL128" t="s" s="2">
+      <c r="AM128" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -16892,10 +16888,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16918,19 +16914,19 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16979,7 +16975,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16988,19 +16984,19 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AJ129" t="s" s="2">
+      <c r="AK129" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AK129" t="s" s="2">
+      <c r="AL129" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL129" t="s" s="2">
+      <c r="AM129" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17008,10 +17004,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17034,17 +17030,17 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17093,7 +17089,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17111,7 +17107,7 @@
         <v>426</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>106</v>
@@ -17122,10 +17118,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17234,10 +17230,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17348,10 +17344,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17377,13 +17373,13 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17433,16 +17429,16 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI133" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17462,10 +17458,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17491,13 +17487,13 @@
         <v>130</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17527,7 +17523,7 @@
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -17545,7 +17541,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17574,10 +17570,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17603,13 +17599,13 @@
         <v>217</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17659,7 +17655,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17677,7 +17673,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -17688,10 +17684,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17717,13 +17713,13 @@
         <v>102</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17773,7 +17769,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17802,10 +17798,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17828,19 +17824,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -17889,7 +17885,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17907,7 +17903,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17918,10 +17914,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18030,10 +18026,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18144,14 +18140,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18173,10 +18169,10 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>112</v>
@@ -18231,7 +18227,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18260,10 +18256,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18289,14 +18285,14 @@
         <v>240</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18324,11 +18320,11 @@
         <v>150</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>78</v>
       </c>
@@ -18345,7 +18341,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18363,7 +18359,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -18374,10 +18370,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18400,17 +18396,17 @@
         <v>78</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18459,7 +18455,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18474,10 +18470,10 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL142" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -18488,10 +18484,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18514,17 +18510,17 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -18573,7 +18569,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18588,10 +18584,10 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AL143" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>78</v>
@@ -18602,10 +18598,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18628,17 +18624,17 @@
         <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -18687,7 +18683,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -18702,10 +18698,10 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL144" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -18716,10 +18712,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18742,17 +18738,17 @@
         <v>78</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -18801,7 +18797,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:15:35+00:00</t>
+    <t>2025-05-12T09:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:44:35+00:00</t>
+    <t>2025-05-12T09:48:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:48:13+00:00</t>
+    <t>2025-05-12T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:07:46+00:00</t>
+    <t>2025-05-12T12:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:08:59+00:00</t>
+    <t>2025-05-12T12:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:21:25+00:00</t>
+    <t>2025-05-12T12:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:41:16+00:00</t>
+    <t>2025-05-12T13:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T13:04:33+00:00</t>
+    <t>2025-05-12T14:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:29:06+00:00</t>
+    <t>2025-05-12T14:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:37:35+00:00</t>
+    <t>2025-05-12T15:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T15:04:22+00:00</t>
+    <t>2025-05-13T10:20:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:20:58+00:00</t>
+    <t>2025-05-20T13:44:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:44:07+00:00</t>
+    <t>2025-05-20T13:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:46:53+00:00</t>
+    <t>2025-05-20T13:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:54:28+00:00</t>
+    <t>2025-05-20T13:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:56:00+00:00</t>
+    <t>2025-05-23T16:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:42:05+00:00</t>
+    <t>2025-05-23T16:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:51:26+00:00</t>
+    <t>2025-05-24T07:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-24T07:13:38+00:00</t>
+    <t>2025-05-26T07:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-add-examples/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T07:36:52+00:00</t>
+    <t>2025-05-28T11:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
